--- a/Documentation/inventario_variables.xlsx
+++ b/Documentation/inventario_variables.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\OneDrive - Universidad del Magdalena\Documentos\DataIcfes_Proyecto1\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\OneDrive - Universidad del Magdalena\Documentos\Project_DataIcfes\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179304C1-071A-4A08-A4F4-00E9127B9CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC73CE3-7F92-4FFC-9678-DA108C9B4656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{668D981F-8B6F-4134-91AF-CF6BA0385014}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="200">
   <si>
     <t>Bloque</t>
   </si>
@@ -395,9 +395,6 @@
     <t>En SB11 cambia de nombre y estructura a partir de 2014-2.</t>
   </si>
   <si>
-    <t>2010-1 a 2014-1 / 2012 -2020, 2021 a 2025</t>
-  </si>
-  <si>
     <t>CORREGIDO: En SB11 el nombre oficial desde 2014-2 es 'punt_sociales_ciudadanas'.</t>
   </si>
   <si>
@@ -452,9 +449,6 @@
     <t>No hay cambio entre Periodos</t>
   </si>
   <si>
-    <t>2010-1 a 2014-1 ,  2014 - 2 a 2025 - 2 / 2012 -2020, 2021 a 2025</t>
-  </si>
-  <si>
     <t>Identificador de desempeño en naturales</t>
   </si>
   <si>
@@ -560,9 +554,6 @@
     <t>NO OFICIAL, OFICIAL / NO OFICIAL - CORPORACIÓN, NO OFICIAL - FUNDACIÓN, OFICIAL DEPARTAMENTAL, OFICIAL MUNICIPAL, OFICIAL NACIONAL, REGIMEN ESPECIAL</t>
   </si>
   <si>
-    <t>2010-1 a 2014-1 ,  2014 - 2 a 2025 - 2 / 2012 -2020, 2021 a 2026</t>
-  </si>
-  <si>
     <t>Identificador de la jornada de la institucion</t>
   </si>
   <si>
@@ -587,18 +578,9 @@
     <t>Identificador de codigo de la IES</t>
   </si>
   <si>
-    <t>Código de la Institución de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educación Superior </t>
-  </si>
-  <si>
     <t xml:space="preserve">Numérica </t>
   </si>
   <si>
-    <t>2012 -2020, 2021 a 2026</t>
-  </si>
-  <si>
     <t>Sin incongruencias detectadas. Variable consistente en SB11.</t>
   </si>
   <si>
@@ -630,13 +612,40 @@
   </si>
   <si>
     <t>Nombre del departamento donde está ubicada la IES</t>
+  </si>
+  <si>
+    <t>estu_prgm_academico</t>
+  </si>
+  <si>
+    <t>estu_snies_prgmacademico</t>
+  </si>
+  <si>
+    <t>Identificador del programa del estudiante</t>
+  </si>
+  <si>
+    <t>Nombre del programa académico que estudia</t>
+  </si>
+  <si>
+    <t>2012 - 2020, 2021 a 2024</t>
+  </si>
+  <si>
+    <t>Código de la Institución de la IES</t>
+  </si>
+  <si>
+    <t>Identificador del programa academico</t>
+  </si>
+  <si>
+    <t>Código SNIES del programa académico que estudia</t>
+  </si>
+  <si>
+    <t>2013 - 2020, 2021 a 2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,6 +664,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1040,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BA8F263-A49F-414F-9424-7621A86EB8BD}">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
@@ -1137,7 +1152,7 @@
         <v>33</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -1342,7 +1357,7 @@
         <v>22</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -1394,7 +1409,7 @@
         <v>61</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>62</v>
@@ -1403,7 +1418,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>18</v>
@@ -1435,7 +1450,7 @@
         <v>64</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>66</v>
@@ -1444,7 +1459,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>18</v>
@@ -1456,7 +1471,7 @@
         <v>19</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>21</v>
@@ -1465,7 +1480,7 @@
         <v>22</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1473,19 +1488,19 @@
         <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>18</v>
@@ -1497,7 +1512,7 @@
         <v>67</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>21</v>
@@ -1506,7 +1521,7 @@
         <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.35">
@@ -1711,7 +1726,7 @@
         <v>22</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="62.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -1825,7 +1840,7 @@
         <v>117</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>21</v>
@@ -1834,7 +1849,7 @@
         <v>22</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -1842,25 +1857,25 @@
         <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>19</v>
@@ -1883,28 +1898,28 @@
         <v>111</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>20</v>
@@ -1916,7 +1931,7 @@
         <v>22</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -1924,19 +1939,19 @@
         <v>111</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>27</v>
@@ -1945,10 +1960,10 @@
         <v>27</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>21</v>
@@ -1965,19 +1980,19 @@
         <v>111</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>28</v>
@@ -1986,10 +2001,10 @@
         <v>28</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>21</v>
@@ -1998,7 +2013,7 @@
         <v>22</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.35">
@@ -2006,31 +2021,31 @@
         <v>111</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>21</v>
@@ -2039,7 +2054,7 @@
         <v>22</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -2047,19 +2062,19 @@
         <v>111</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>28</v>
@@ -2068,10 +2083,10 @@
         <v>28</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>21</v>
@@ -2080,7 +2095,7 @@
         <v>22</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="29" x14ac:dyDescent="0.35">
@@ -2088,19 +2103,19 @@
         <v>111</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>28</v>
@@ -2109,10 +2124,10 @@
         <v>28</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>21</v>
@@ -2121,27 +2136,27 @@
         <v>22</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="48" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>18</v>
@@ -2150,10 +2165,10 @@
         <v>18</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>21</v>
@@ -2162,39 +2177,39 @@
         <v>33</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="97.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>21</v>
@@ -2208,34 +2223,34 @@
     </row>
     <row r="29" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>21</v>
@@ -2244,39 +2259,39 @@
         <v>33</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>182</v>
+      <c r="F30" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>21</v>
@@ -2294,9 +2309,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="7"/>
-      <c r="F31" s="5" t="s">
-        <v>183</v>
-      </c>
+      <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -2305,8 +2318,91 @@
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
     </row>
+    <row r="32" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="F30:F31"/>
     <mergeCell ref="M30:M31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
@@ -2320,6 +2416,7 @@
     <mergeCell ref="K30:K31"/>
     <mergeCell ref="L30:L31"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
